--- a/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>REINA DE LOS ANGELES DE MANCHAY</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.09486</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.8848</v>
-      </c>
-      <c r="I2" t="n">
-        <v>91</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.09486</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.8848</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>527 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.2289</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.85818</v>
-      </c>
-      <c r="I3" t="n">
-        <v>242</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.2289</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.85818</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>653</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.11151</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.87503</v>
-      </c>
-      <c r="I4" t="n">
-        <v>226</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.11151</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.87503</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>667</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.09988</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.87475999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>357</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.09988</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.87476</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>668 ROXANITA CASTRO WITTING / 7263 ROXANITA CASTRO WITTING</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.12297</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.87164</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1072</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.12297</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.87164</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>6028 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.18758</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.86708</v>
-      </c>
-      <c r="I7" t="n">
-        <v>585</v>
-      </c>
-      <c r="J7" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.18758</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.86708</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>6006 SANTISIMA VIRGEN DE LOURDES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.22828</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.85886000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>726</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.22828</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.85886</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>6007</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.22942</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.85912</v>
-      </c>
-      <c r="I9" t="n">
-        <v>819</v>
-      </c>
-      <c r="J9" t="n">
-        <v>41</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.22942</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.85912</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>6100 SANTA MARIA REYNA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.20992</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.87457000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>352</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.20992</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.87457</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>ISAIAS ARDILES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.22935</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.85760999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1039</v>
-      </c>
-      <c r="J11" t="n">
-        <v>56</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.22935</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.85761</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>672</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.09551</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.88687</v>
-      </c>
-      <c r="I12" t="n">
-        <v>265</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.09551</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.88687</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>7262 MI NUEVO PERU</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.08484</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.87376</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1160</v>
-      </c>
-      <c r="J13" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.08484</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.87376</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>SANTISIMA VIRGEN DIVINA PASTORA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.1116</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.86699</v>
-      </c>
-      <c r="I14" t="n">
-        <v>419</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.1116</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.86699</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>SEÑOR DE LA ASCENSION</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.0989</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.87053</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1282</v>
-      </c>
-      <c r="J15" t="n">
-        <v>41</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.0989</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.87053</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>MONITOR HUASCAR</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.11681</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.87108000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>643</v>
-      </c>
-      <c r="J16" t="n">
-        <v>37</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.11681</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.87108</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.11114</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.87486</v>
-      </c>
-      <c r="I17" t="n">
-        <v>297</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.11114</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.87486</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SAN SALVADOR</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.22911</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.85833</v>
-      </c>
-      <c r="I18" t="n">
-        <v>790</v>
-      </c>
-      <c r="J18" t="n">
-        <v>37</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.22911</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.85833</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.12471</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.87635</v>
-      </c>
-      <c r="I19" t="n">
-        <v>93</v>
-      </c>
-      <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.12471</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.87635</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>JOSE MARIA ARGUEDAS DE MANCHAY</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.10461</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.87568</v>
-      </c>
-      <c r="I20" t="n">
-        <v>188</v>
-      </c>
-      <c r="J20" t="n">
-        <v>13</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.10461</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.87568</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>SAN LORENZO DE MANCHAY</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.10053</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.87981000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>275</v>
-      </c>
-      <c r="J21" t="n">
-        <v>15</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.10053</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.87981</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>SAN FERNANDO DE PACHACAMAC</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.2132</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.84921</v>
-      </c>
-      <c r="I22" t="n">
-        <v>235</v>
-      </c>
-      <c r="J22" t="n">
-        <v>22</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.2132</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.84921</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>SAN ISIDRO DE MANCHAY</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.11482</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.87412999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>869</v>
-      </c>
-      <c r="J23" t="n">
-        <v>48</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.11482</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.87413</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SANTA ROSA DE LA MESETA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.10706</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.86060999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>42</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.10706</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.86061</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SAN AGUSTIN DE PACHACAMAC</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.15306</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.86933999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>232</v>
-      </c>
-      <c r="J25" t="n">
-        <v>16</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.15306</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.86934</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>SANTA MARIA REINA DEL MUNDO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.09814</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.87475000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>481</v>
-      </c>
-      <c r="J26" t="n">
-        <v>24</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.09814</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.87475</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>LOS JARDINES DE MANCHAY</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.151</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.8903</v>
-      </c>
-      <c r="I27" t="n">
-        <v>824</v>
-      </c>
-      <c r="J27" t="n">
-        <v>31</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.151</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.8903</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SANTISIMO JESUS SALVADOR</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.23154</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.85905</v>
-      </c>
-      <c r="I28" t="n">
-        <v>210</v>
-      </c>
-      <c r="J28" t="n">
-        <v>12</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.23154</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.85905</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>CARRUSEL</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.22887</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.85879</v>
-      </c>
-      <c r="I29" t="n">
-        <v>138</v>
-      </c>
-      <c r="J29" t="n">
-        <v>9</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.22887</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.85879</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>EL UNIVERSO DE CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.08358</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.87940999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>291</v>
-      </c>
-      <c r="J30" t="n">
-        <v>22</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.08358</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.87941</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>EUROAMERICAN COLLEGE</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.22007</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.87101</v>
-      </c>
-      <c r="I31" t="n">
-        <v>597</v>
-      </c>
-      <c r="J31" t="n">
-        <v>82</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.22007</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.87101</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>7265</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.09596</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.88479</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1319</v>
-      </c>
-      <c r="J32" t="n">
-        <v>52</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.09596</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.88479</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>SAN JOSE DE MANCHAY</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.09941</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.87729</v>
-      </c>
-      <c r="I33" t="n">
-        <v>107</v>
-      </c>
-      <c r="J33" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.09941</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.87729</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>NUESTRA SEÑORA ESTRELLA DE LA EVANGELIZACION</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.10978</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.86221999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>108</v>
-      </c>
-      <c r="J34" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.10978</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.86222</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>675 LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.1005</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.88415999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>200</v>
-      </c>
-      <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.1005</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.88416</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>7263 ROXANITA CASTRO WITTING</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.12307</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.87163</v>
-      </c>
-      <c r="I36" t="n">
-        <v>665</v>
-      </c>
-      <c r="J36" t="n">
-        <v>29</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.12307</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.87163</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>MADRE NICOLETTA GATTI</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.22374</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.84672999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>38</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.22374</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.84673</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SINAI</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.08738</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.87336000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>348</v>
-      </c>
-      <c r="J38" t="n">
-        <v>24</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.08738</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.87336</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>CIENCIA Y TECNOLOGIA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.10033</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.87804</v>
-      </c>
-      <c r="I39" t="n">
-        <v>116</v>
-      </c>
-      <c r="J39" t="n">
-        <v>8</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.10033</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.87804</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.22641</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.85921</v>
-      </c>
-      <c r="I40" t="n">
-        <v>429</v>
-      </c>
-      <c r="J40" t="n">
-        <v>17</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.22641</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.85921</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>TRINITY SCHOOL</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.20003</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.87403999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>103</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.20003</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.87404</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SANTISIMA VIRGEN INMACULADA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.12834</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.87121</v>
-      </c>
-      <c r="I42" t="n">
-        <v>216</v>
-      </c>
-      <c r="J42" t="n">
-        <v>15</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.12834</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.87121</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>LICEO SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.12702</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.87322</v>
-      </c>
-      <c r="I43" t="n">
-        <v>367</v>
-      </c>
-      <c r="J43" t="n">
-        <v>35</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.12702</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.87322</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,24 +3113,530 @@
           <t>DIVER HOUSE</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.10362</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.8753</v>
-      </c>
-      <c r="I44" t="n">
-        <v>36</v>
-      </c>
-      <c r="J44" t="n">
-        <v>4</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.10362</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.8753</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>318107</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>662 REINA DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.20985</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.87658</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>318112</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>663 DIVINO NIÑO DEL MILAGRO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.18656</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.86943</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>318150</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.1579</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-76.86958</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>318249</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>7040 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.19956</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.87261</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>688293</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PAUL SABATIER</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.10899</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.86968</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>777703</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BELLA ESMERALDA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.10805</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.88056</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>797843</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BEATO JUAN XXIII</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.09926</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.88896</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>150123</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PACHACAMAC</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>834727</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NIÑO REY</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.144</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.8728</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>294818</t>
+          <t>318065</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>REINA DE LOS ANGELES DE MANCHAY</t>
+          <t>653</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.09486</t>
+          <t>-12.11151</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.8848</t>
+          <t>-76.87503</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>318065</t>
+          <t>318329</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>672</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.11151</t>
+          <t>-12.09551</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.87503</t>
+          <t>-76.88687</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>318131</t>
+          <t>318353</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>SANTISIMA VIRGEN DIVINA PASTORA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.09988</t>
+          <t>-12.1116</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.87476</t>
+          <t>-76.86699</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>318145</t>
+          <t>649579</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>668 ROXANITA CASTRO WITTING / 7263 ROXANITA CASTRO WITTING</t>
+          <t>SANTISIMO JESUS SALVADOR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.12297</t>
+          <t>-12.23154</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.87164</t>
+          <t>-76.85905</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>318174</t>
+          <t>318485</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6028 JUAN VELASCO ALVARADO</t>
+          <t>JOSE MARIA ARGUEDAS DE MANCHAY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.18758</t>
+          <t>-12.10461</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.86708</t>
+          <t>-76.87568</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>188</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>318206</t>
+          <t>318131</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6006 SANTISIMA VIRGEN DE LOURDES</t>
+          <t>667</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.22828</t>
+          <t>-12.09988</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.85886</t>
+          <t>-76.87476</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>318211</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>SAN LORENZO DE MANCHAY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.22942</t>
+          <t>-12.10053</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.85912</t>
+          <t>-76.87981</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>318230</t>
+          <t>805758</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6100 SANTA MARIA REYNA</t>
+          <t>SANTISIMA VIRGEN INMACULADA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.20992</t>
+          <t>-12.12834</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.87457</t>
+          <t>-76.87121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>318305</t>
+          <t>591088</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ISAIAS ARDILES</t>
+          <t>SAN AGUSTIN DE PACHACAMAC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.22935</t>
+          <t>-12.15306</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.85761</t>
+          <t>-76.86934</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>318329</t>
+          <t>318230</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>6100 SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.09551</t>
+          <t>-12.20992</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.88687</t>
+          <t>-76.87457</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>352</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>318334</t>
+          <t>782931</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7262 MI NUEVO PERU</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.08484</t>
+          <t>-12.22641</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.87376</t>
+          <t>-76.85921</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>429</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>318353</t>
+          <t>318391</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DIVINA PASTORA</t>
+          <t>VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.1116</t>
+          <t>-12.11114</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.86699</t>
+          <t>-76.87486</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>297</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>318367</t>
+          <t>479888</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA ASCENSION</t>
+          <t>SAN FERNANDO DE PACHACAMAC</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.0989</t>
+          <t>-12.2132</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.87053</t>
+          <t>-76.84921</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>318386</t>
+          <t>686717</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MONITOR HUASCAR</t>
+          <t>EL UNIVERSO DE CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.11681</t>
+          <t>-12.08358</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.87108</t>
+          <t>-76.87941</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>318391</t>
+          <t>597641</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA PUERTA</t>
+          <t>SANTA MARIA REINA DEL MUNDO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.11114</t>
+          <t>-12.09814</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.87486</t>
+          <t>-76.87475</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>481</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>318414</t>
+          <t>743204</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAN SALVADOR</t>
+          <t>SINAI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.22911</t>
+          <t>-12.08738</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.85833</t>
+          <t>-76.87336</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>318452</t>
+          <t>318174</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>6028 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.12471</t>
+          <t>-12.18758</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.87635</t>
+          <t>-76.86708</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>585</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>318485</t>
+          <t>717629</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS DE MANCHAY</t>
+          <t>7263 ROXANITA CASTRO WITTING</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.10461</t>
+          <t>-12.12307</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.87568</t>
+          <t>-76.87163</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>665</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>580645</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SAN LORENZO DE MANCHAY</t>
+          <t>SANTA ROSA DE LA MESETA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.10053</t>
+          <t>-12.10706</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.87981</t>
+          <t>-76.86061</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>479888</t>
+          <t>318206</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN FERNANDO DE PACHACAMAC</t>
+          <t>6006 SANTISIMA VIRGEN DE LOURDES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.2132</t>
+          <t>-12.22828</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.84921</t>
+          <t>-76.85886</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>726</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>552303</t>
+          <t>611270</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN ISIDRO DE MANCHAY</t>
+          <t>LOS JARDINES DE MANCHAY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.11482</t>
+          <t>-12.151</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.87413</t>
+          <t>-76.8903</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>824</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>580645</t>
+          <t>836062</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LA MESETA</t>
+          <t>LICEO SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.10706</t>
+          <t>-12.12702</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.86061</t>
+          <t>-76.87322</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>591088</t>
+          <t>318386</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE PACHACAMAC</t>
+          <t>MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.15306</t>
+          <t>-12.11681</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.86934</t>
+          <t>-76.87108</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>643</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>597641</t>
+          <t>318414</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANTA MARIA REINA DEL MUNDO</t>
+          <t>SAN SALVADOR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.09814</t>
+          <t>-12.22911</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.87475</t>
+          <t>-76.85833</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>790</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>611270</t>
+          <t>294818</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LOS JARDINES DE MANCHAY</t>
+          <t>REINA DE LOS ANGELES DE MANCHAY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.151</t>
+          <t>-12.09486</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.8903</t>
+          <t>-76.8848</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>649579</t>
+          <t>687967</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANTISIMO JESUS SALVADOR</t>
+          <t>SAN JOSE DE MANCHAY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.23154</t>
+          <t>-12.09941</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.85905</t>
+          <t>-76.87729</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,42 +2175,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>686557</t>
+          <t>688009</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CARRUSEL</t>
+          <t>NUESTRA SEÑORA ESTRELLA DE LA EVANGELIZACION</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.22887</t>
+          <t>-12.10978</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.85879</t>
+          <t>-76.86222</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>686717</t>
+          <t>733629</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EL UNIVERSO DE CESAR VALLEJO</t>
+          <t>MADRE NICOLETTA GATTI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.08358</t>
+          <t>-12.22374</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.87941</t>
+          <t>-76.84673</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,42 +2299,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>686835</t>
+          <t>845684</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EUROAMERICAN COLLEGE</t>
+          <t>DIVER HOUSE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.22007</t>
+          <t>-12.10362</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.87101</t>
+          <t>-76.8753</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>687533</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7262 MI NUEVO PERU</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.09596</t>
+          <t>-12.08484</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.88479</t>
+          <t>-76.87376</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>687967</t>
+          <t>318145</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAN JOSE DE MANCHAY</t>
+          <t>668 ROXANITA CASTRO WITTING / 7263 ROXANITA CASTRO WITTING</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.09941</t>
+          <t>-12.12297</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.87729</t>
+          <t>-76.87164</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>688009</t>
+          <t>318211</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA ESTRELLA DE LA EVANGELIZACION</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.10978</t>
+          <t>-12.22942</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.86222</t>
+          <t>-76.85912</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>819</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>688405</t>
+          <t>318367</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>675 LAS MERCEDES</t>
+          <t>SEÑOR DE LA ASCENSION</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.1005</t>
+          <t>-12.0989</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.88416</t>
+          <t>-76.87053</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,42 +2609,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>717629</t>
+          <t>552303</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7263 ROXANITA CASTRO WITTING</t>
+          <t>SAN ISIDRO DE MANCHAY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.12307</t>
+          <t>-12.11482</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.87163</t>
+          <t>-76.87413</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>869</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>733629</t>
+          <t>687533</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MADRE NICOLETTA GATTI</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.22374</t>
+          <t>-12.09596</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.84673</t>
+          <t>-76.88479</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>743204</t>
+          <t>318305</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SINAI</t>
+          <t>ISAIAS ARDILES</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.08738</t>
+          <t>-12.22935</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.87336</t>
+          <t>-76.85761</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,42 +2795,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>749913</t>
+          <t>318452</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CIENCIA Y TECNOLOGIA</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.10033</t>
+          <t>-12.12471</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.87804</t>
+          <t>-76.87635</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,42 +2857,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>782931</t>
+          <t>749913</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>CIENCIA Y TECNOLOGIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.22641</t>
+          <t>-12.10033</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.85921</t>
+          <t>-76.87804</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>786665</t>
+          <t>686835</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRINITY SCHOOL</t>
+          <t>EUROAMERICAN COLLEGE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.20003</t>
+          <t>-12.22007</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.87404</t>
+          <t>-76.87101</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>597</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>805758</t>
+          <t>686557</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN INMACULADA</t>
+          <t>CARRUSEL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.12834</t>
+          <t>-12.22887</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.87121</t>
+          <t>-76.85879</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>836062</t>
+          <t>688405</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LICEO SAN MARTIN DE PORRES</t>
+          <t>675 LAS MERCEDES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.12702</t>
+          <t>-12.1005</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.87322</t>
+          <t>-76.88416</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>845684</t>
+          <t>786665</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DIVER HOUSE</t>
+          <t>TRINITY SCHOOL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.10362</t>
+          <t>-12.20003</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.8753</t>
+          <t>-76.87404</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -1627,12 +1627,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.12307</t>
+          <t>-12.11989</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.87163</t>
+          <t>-76.87138</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>318065</t>
+          <t>845684</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>DIVER HOUSE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.11151</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.87503</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.10362</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.8753</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>318051</t>
+          <t>836062</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>527 NIÑO JESUS DE PRAGA</t>
+          <t>LICEO SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.2289</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.85818</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-12.12702</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.87322</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>318329</t>
+          <t>834727</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>NIÑO REY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.09551</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.88687</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-12.144</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.8728</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>318353</t>
+          <t>805758</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DIVINA PASTORA</t>
+          <t>SANTISIMA VIRGEN INMACULADA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.1116</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.86699</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>-12.12834</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.87121</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>649579</t>
+          <t>797843</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANTISIMO JESUS SALVADOR</t>
+          <t>BEATO JUAN XXIII</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.23154</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.85905</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-12.09926</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.88896</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,42 +811,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>318485</t>
+          <t>786665</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS DE MANCHAY</t>
+          <t>TRINITY SCHOOL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.10461</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.87568</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>-12.20003</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.87404</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>318131</t>
+          <t>782931</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.09988</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.87476</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-12.22641</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.85921</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>777703</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN LORENZO DE MANCHAY</t>
+          <t>BELLA ESMERALDA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.10053</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.87981</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-12.10805</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.88056</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>805758</t>
+          <t>749913</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN INMACULADA</t>
+          <t>CIENCIA Y TECNOLOGIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.12834</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.87121</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-12.10033</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.87804</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>591088</t>
+          <t>743204</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE PACHACAMAC</t>
+          <t>SINAI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.15306</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.86934</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-12.08738</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.87336</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>318230</t>
+          <t>733629</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6100 SANTA MARIA REYNA</t>
+          <t>MADRE NICOLETTA GATTI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.20992</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.87457</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>-12.22374</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.84673</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>782931</t>
+          <t>717629</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>7263 ROXANITA CASTRO WITTING</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.22641</t>
+          <t>665</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.85921</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>-12.11989</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.87138</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>318391</t>
+          <t>688405</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA PUERTA</t>
+          <t>675 LAS MERCEDES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.11114</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.87486</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>-12.1005</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.88416</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>479888</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN FERNANDO DE PACHACAMAC</t>
+          <t>PAUL SABATIER</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.2132</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.84921</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-12.10899</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.86968</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>686717</t>
+          <t>688009</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EL UNIVERSO DE CESAR VALLEJO</t>
+          <t>NUESTRA SEÑORA ESTRELLA DE LA EVANGELIZACION</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.08358</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.87941</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-12.10978</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.86222</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>597641</t>
+          <t>687967</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA MARIA REINA DEL MUNDO</t>
+          <t>SAN JOSE DE MANCHAY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.09814</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.87475</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>-12.09941</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.87729</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>743204</t>
+          <t>687533</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SINAI</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.08738</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.87336</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-12.09596</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.88479</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>318174</t>
+          <t>686835</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6028 JUAN VELASCO ALVARADO</t>
+          <t>EUROAMERICAN COLLEGE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.18758</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.86708</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>-12.22007</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.87101</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,42 +1617,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>717629</t>
+          <t>686717</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7263 ROXANITA CASTRO WITTING</t>
+          <t>EL UNIVERSO DE CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.11989</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.87138</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>-12.08358</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.87941</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,42 +1679,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>580645</t>
+          <t>686557</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LA MESETA</t>
+          <t>CARRUSEL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.10706</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.86061</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-12.22887</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.85879</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>318206</t>
+          <t>649579</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6006 SANTISIMA VIRGEN DE LOURDES</t>
+          <t>SANTISIMO JESUS SALVADOR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.22828</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.85886</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>-12.23154</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.85905</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1813,22 +1813,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>-12.151</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-76.8903</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>836062</t>
+          <t>597641</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LICEO SAN MARTIN DE PORRES</t>
+          <t>SANTA MARIA REINA DEL MUNDO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.12702</t>
+          <t>481</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.87322</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-12.09814</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.87475</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>318386</t>
+          <t>591088</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MONITOR HUASCAR</t>
+          <t>SAN AGUSTIN DE PACHACAMAC</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.11681</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.87108</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>-12.15306</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.86934</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>318414</t>
+          <t>580645</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAN SALVADOR</t>
+          <t>SANTA ROSA DE LA MESETA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.22911</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.85833</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>-12.10706</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.86061</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>294818</t>
+          <t>552303</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>REINA DE LOS ANGELES DE MANCHAY</t>
+          <t>SAN ISIDRO DE MANCHAY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.09486</t>
+          <t>869</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.8848</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-12.11482</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.87413</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>687967</t>
+          <t>479888</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAN JOSE DE MANCHAY</t>
+          <t>SAN FERNANDO DE PACHACAMAC</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.09941</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.87729</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>-12.2132</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.84921</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>688009</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA ESTRELLA DE LA EVANGELIZACION</t>
+          <t>SAN LORENZO DE MANCHAY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.10978</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.86222</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>-12.10053</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.87981</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,42 +2237,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>733629</t>
+          <t>318485</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MADRE NICOLETTA GATTI</t>
+          <t>JOSE MARIA ARGUEDAS DE MANCHAY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.22374</t>
+          <t>188</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.84673</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-12.10461</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.87568</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>845684</t>
+          <t>318452</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DIVER HOUSE</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.10362</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.8753</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-12.12471</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.87635</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>318334</t>
+          <t>318414</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7262 MI NUEVO PERU</t>
+          <t>SAN SALVADOR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.08484</t>
+          <t>790</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.87376</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>-12.22911</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.85833</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,42 +2423,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>318145</t>
+          <t>318391</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>668 ROXANITA CASTRO WITTING / 7263 ROXANITA CASTRO WITTING</t>
+          <t>VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.12297</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.87164</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>-12.11114</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.87486</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>318211</t>
+          <t>318386</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.22942</t>
+          <t>643</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.85912</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>-12.11681</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.87108</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2557,22 +2557,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>-12.0989</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-76.87053</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>552303</t>
+          <t>318353</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN ISIDRO DE MANCHAY</t>
+          <t>SANTISIMA VIRGEN DIVINA PASTORA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.11482</t>
+          <t>419</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.87413</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>-12.1116</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.86699</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>687533</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7262 MI NUEVO PERU</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.09596</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.88479</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>-12.08484</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.87376</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>318305</t>
+          <t>318329</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ISAIAS ARDILES</t>
+          <t>672</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.22935</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.85761</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>-12.09551</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-76.88687</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>318452</t>
+          <t>318305</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>ISAIAS ARDILES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.12471</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.87635</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>-12.22935</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-76.85761</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,37 +2857,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>749913</t>
+          <t>318249</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CIENCIA Y TECNOLOGIA</t>
+          <t>7040 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.10033</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.87804</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-12.19956</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.87261</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>686835</t>
+          <t>318230</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EUROAMERICAN COLLEGE</t>
+          <t>6100 SANTA MARIA REYNA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.22007</t>
+          <t>352</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.87101</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>-12.20992</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-76.87457</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>686557</t>
+          <t>318211</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CARRUSEL</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.22887</t>
+          <t>819</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.85879</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>-12.22942</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.85912</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>688405</t>
+          <t>318206</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>675 LAS MERCEDES</t>
+          <t>6006 SANTISIMA VIRGEN DE LOURDES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.1005</t>
+          <t>726</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.88416</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-12.22828</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.85886</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>786665</t>
+          <t>318174</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TRINITY SCHOOL</t>
+          <t>6028 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.20003</t>
+          <t>585</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.87404</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-12.18758</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.86708</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>318107</t>
+          <t>318150</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>662 REINA DE LOS ANGELES</t>
+          <t>669</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.20985</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.87658</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-12.1579</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.86958</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,42 +3229,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>318112</t>
+          <t>318145</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>663 DIVINO NIÑO DEL MILAGRO</t>
+          <t>668 ROXANITA CASTRO WITTING / 7263 ROXANITA CASTRO WITTING</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.18656</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.86943</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>-12.12297</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.87164</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>318150</t>
+          <t>318131</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>667</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.1579</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.86958</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>-12.09988</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.87476</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>318249</t>
+          <t>318112</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7040 SAN MARTIN DE PORRES</t>
+          <t>663 DIVINO NIÑO DEL MILAGRO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.19956</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.87261</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>-12.18656</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.86943</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>688293</t>
+          <t>318107</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PAUL SABATIER</t>
+          <t>662 REINA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.10899</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.86968</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-12.20985</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.87658</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>777703</t>
+          <t>318065</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BELLA ESMERALDA</t>
+          <t>653</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.10805</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.88056</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-12.11151</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-76.87503</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>797843</t>
+          <t>318051</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BEATO JUAN XXIII</t>
+          <t>527 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.09926</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.88896</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-12.2289</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-76.85818</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>834727</t>
+          <t>294818</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NIÑO REY</t>
+          <t>REINA DE LOS ANGELES DE MANCHAY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.144</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.8728</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-12.09486</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.8848</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-PACHACAMAC.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
